--- a/data/freelance-platforms.xlsx
+++ b/data/freelance-platforms.xlsx
@@ -1,34 +1,145 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Makled\Desktop\portfolio, cv\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6472D1E-0E0A-4DF6-8C6A-36F9CB489555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>PlatformName</t>
+  </si>
+  <si>
+    <t>LogoPath</t>
+  </si>
+  <si>
+    <t>ProfileURL</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Upwork</t>
+  </si>
+  <si>
+    <t>Mostaql</t>
+  </si>
+  <si>
+    <t>https://mostaql.com/u/ahmed1makled1</t>
+  </si>
+  <si>
+    <t>Arabic freelance marketplace profile offering Flutter mobile app development and software engineering services.</t>
+  </si>
+  <si>
+    <t>Khamsat</t>
+  </si>
+  <si>
+    <t>https://khamsat.com/user/ahmed1makled1</t>
+  </si>
+  <si>
+    <t>Arabic microservices marketplace profile for Flutter development, bug fixing, and mobile solutions.</t>
+  </si>
+  <si>
+    <t>Nafezly</t>
+  </si>
+  <si>
+    <t>https://nafezly.com/u/ahmedmakled</t>
+  </si>
+  <si>
+    <t>Freelance profile showcasing mobile application development and software engineering services.</t>
+  </si>
+  <si>
+    <t>Kafiil</t>
+  </si>
+  <si>
+    <t>https://kafiil.com/u/ahmedmakled</t>
+  </si>
+  <si>
+    <t>Freelance marketplace profile providing Flutter and cross-platform mobile development services.</t>
+  </si>
+  <si>
+    <t>https://www.upwork.com/freelancers/~01c2d899850e25e266?mp_source=share</t>
+  </si>
+  <si>
+    <t>Professional Upwork profile for cross-platform mobile application development with Flutter and Firebase.</t>
+  </si>
+  <si>
+    <t>Freelance Yard</t>
+  </si>
+  <si>
+    <t>https://freelanceyard.com/en/freelancers/ahmed-makled</t>
+  </si>
+  <si>
+    <t>International freelancer profile featuring Flutter, mobile app development, and software engineering expertise.</t>
+  </si>
+  <si>
+    <t>/assets/logos/Kafiil.jpg</t>
+  </si>
+  <si>
+    <t>/assets/logos/Khamsat.png</t>
+  </si>
+  <si>
+    <t>/assets/logos/Mostaql.png</t>
+  </si>
+  <si>
+    <t>/assets/logos/Nafezly.png</t>
+  </si>
+  <si>
+    <t>/assets/logos/Upwork.png</t>
+  </si>
+  <si>
+    <t>/assets/logos/Freelance Yard.jpg</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -43,84 +154,36 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,103 +471,123 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="3" max="3" width="40.42578125" customWidth="1"/>
+    <col min="4" max="4" width="72.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>PlatformName</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>LogoPath</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>ProfileURL</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Upwork</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://www.upwork.com/freelancers/~</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Professional freelance profile with verified skills and client reviews.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Freelancer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://www.freelancer.com/u/</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Freelance marketplace profile showcasing mobile development projects.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Fiverr</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>assets/images/profile.jpg</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>https://www.fiverr.com/</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gig-based services for Flutter development and mobile app consulting.</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="30">
+      <c r="A4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="30">
+      <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{DFD67240-1B92-42D4-A03B-76A53659C9F9}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{7D423573-F059-4FF7-B5A0-2FD04A21EEDD}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{6A6E2794-A54A-4BDA-9269-608D6298A4EA}"/>
+    <hyperlink ref="C7" r:id="rId4" xr:uid="{D3D2CD85-E138-4ABD-A145-A2ED960EEA0A}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{11E37340-3345-4560-B6A5-FBE3FAB3BAE1}"/>
+    <hyperlink ref="C5" r:id="rId6" xr:uid="{5ED3F0EA-7E04-4363-9483-1A28BD04DF9B}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>